--- a/output/가계부.xlsx
+++ b/output/가계부.xlsx
@@ -603,6 +603,11 @@
       <c r="F5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>[갓성비]카츠 ONLY BOX (컷팅X) [감동적 부드러움] 히레카츠 [극강 풍미] 갈릭마제소바(우동면)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -888,6 +893,11 @@
       <c r="F15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>텐돈 포 A6 메인즈 점보세트 R4 파인애플</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -994,6 +1004,11 @@
       <c r="F19" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>동원)덴마크바나바나우유300ml 정화)왕오</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1018,6 +1033,11 @@
       <c r="F20" s="4" t="n">
         <v>21850</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>동원)덴마크바나바나우유300ml 정화)왕오</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1042,6 +1062,11 @@
       <c r="F21" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>동원)덴마크딸기딸기우유300ml 동원)덴마</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1240,6 +1265,11 @@
       <c r="F28" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>서오릉네가지맛피자 L</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1467,6 +1497,11 @@
       <c r="F36" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>리뷰 이벤트 참여 바다의여왕 참돔</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1491,6 +1526,11 @@
       <c r="F37" s="4" t="n">
         <v>70100</v>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>광어 리뷰 이벤트 참여</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1515,6 +1555,11 @@
       <c r="F38" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>광어 리뷰 이벤트 참여</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2090,6 +2135,11 @@
       <c r="F58" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>카라멜 팝콘 프레첼 블루베리 마블 치즈</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2665,6 +2715,11 @@
       <c r="F78" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>페이머스 글레이즈드 클래식 올드훼션드</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3037,6 +3092,11 @@
       <c r="F91" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>소시지 에그 맥머핀 핫케익?2조각 아이스</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3264,6 +3324,11 @@
       <c r="F99" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>불고기오븐스파게티 M+M 미디움2판_가성비</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3839,6 +3904,11 @@
       <c r="F119" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>피치 딸기 피지오 아이스 스타벅스 클래식</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3863,6 +3933,11 @@
       <c r="F120" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>모닝글로리 볶음 텐돈 포 A7 오리지널 스</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3916,6 +3991,11 @@
       <c r="F122" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>특양볶음밥 꽉찬 소곱창구이 1인분 200g</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4490,6 +4570,11 @@
       </c>
       <c r="F142" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>파인트 파인트 크림치즈 아이스 모찌?</t>
+        </is>
       </c>
     </row>
     <row r="143">
